--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-28.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T6"/>
+  <dimension ref="A1:T7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -836,15 +836,19 @@
       <c r="K5" t="n">
         <v>1.51</v>
       </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -918,15 +922,19 @@
       <c r="K6" t="n">
         <v>1.54</v>
       </c>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>AO Away Win</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -950,6 +958,88 @@
       </c>
       <c r="T6" t="n">
         <v>31.83</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Serbian Super League</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Radnicki Nis x Partizan Belgrade</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Radnicki Nis</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Partizan Belgrade</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>379</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>200</v>
+      </c>
+      <c r="S7" t="n">
+        <v>35.71</v>
+      </c>
+      <c r="T7" t="n">
+        <v>34.1</v>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-28.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T7"/>
+  <dimension ref="A1:T10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1008,15 +1008,19 @@
       <c r="K7" t="n">
         <v>1.6</v>
       </c>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1040,6 +1044,252 @@
       </c>
       <c r="T7" t="n">
         <v>34.1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Norwegian Cup</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Pors x Kongsvinger</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Pors</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kongsvinger</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>282</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>200</v>
+      </c>
+      <c r="S8" t="n">
+        <v>32.26</v>
+      </c>
+      <c r="T8" t="n">
+        <v>30.81</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Slovakian Super League</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Trencin x Slovan Bratislava</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Trencin</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Slovan Bratislava</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>200</v>
+      </c>
+      <c r="S9" t="n">
+        <v>32.26</v>
+      </c>
+      <c r="T9" t="n">
+        <v>30.81</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Italian Serie A</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Venezia x Inter Milan</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Inter Milan</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>24496</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>200</v>
+      </c>
+      <c r="S10" t="n">
+        <v>38.46</v>
+      </c>
+      <c r="T10" t="n">
+        <v>36.73</v>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-28.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T10"/>
+  <dimension ref="A1:T16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1094,15 +1094,19 @@
       <c r="K8" t="n">
         <v>1.45</v>
       </c>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1176,15 +1180,19 @@
       <c r="K9" t="n">
         <v>1.51</v>
       </c>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1258,15 +1266,19 @@
       <c r="K10" t="n">
         <v>1.39</v>
       </c>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1290,6 +1302,510 @@
       </c>
       <c r="T10" t="n">
         <v>36.73</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Dutch Cup</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>MVV Maastricht x Excelsior</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>MVV Maastricht</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Excelsior</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>✅ LIQUIDADO</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>334</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>200</v>
+      </c>
+      <c r="S11" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="T11" t="n">
+        <v>29.84</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Danish Cup</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Roskilde x AGF</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Roskilde</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>AGF</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>✅ LIQUIDADO</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>520</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>200</v>
+      </c>
+      <c r="S12" t="n">
+        <v>29.41</v>
+      </c>
+      <c r="T12" t="n">
+        <v>28.09</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Polish Cup</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Lechia Gdansk x Jagiellonia Bialystock</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Lechia Gdansk</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Jagiellonia Bialystock</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>AO Away Win</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>✅ LIQUIDADO</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>294</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>200</v>
+      </c>
+      <c r="S13" t="n">
+        <v>37.04</v>
+      </c>
+      <c r="T13" t="n">
+        <v>35.37</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Scottish Premiership</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Celtic x Dundee Utd</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Celtic</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Dundee Utd</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>7</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>2362</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>200</v>
+      </c>
+      <c r="S14" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="T14" t="n">
+        <v>31.83</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Italian Serie A</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AC Monza x Napoli</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AC Monza</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Napoli</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>8239</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>200</v>
+      </c>
+      <c r="S15" t="n">
+        <v>37.04</v>
+      </c>
+      <c r="T15" t="n">
+        <v>35.37</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>German Cup</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Holstein Kiel x Hoffenheim</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Holstein Kiel</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Hoffenheim</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lay Home/DC X2 (FavVis &lt;= 1.65)</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>1839</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="R16" t="n">
+        <v>200</v>
+      </c>
+      <c r="S16" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="T16" t="n">
+        <v>32.93</v>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-28.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T16"/>
+  <dimension ref="A1:T17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1610,15 +1610,19 @@
       <c r="K14" t="n">
         <v>1.29</v>
       </c>
-      <c r="L14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1692,15 +1696,19 @@
       <c r="K15" t="n">
         <v>1.6</v>
       </c>
-      <c r="L15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>AO Away Win</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1774,15 +1782,19 @@
       <c r="K16" t="n">
         <v>1.51</v>
       </c>
-      <c r="L16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1806,6 +1818,88 @@
       </c>
       <c r="T16" t="n">
         <v>32.93</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Red Bull Bragantino x Chapecoense</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Red Bull Bragantino</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Chapecoense</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>7</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>530</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="R17" t="n">
+        <v>200</v>
+      </c>
+      <c r="S17" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="T17" t="n">
+        <v>31.83</v>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-28.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-28.xlsx
@@ -1868,15 +1868,19 @@
       <c r="K17" t="n">
         <v>1.31</v>
       </c>
-      <c r="L17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
